--- a/reports/2026-10-06_Collateral_Report.xlsx
+++ b/reports/2026-10-06_Collateral_Report.xlsx
@@ -35,7 +35,7 @@
     <t>Overall Cover</t>
   </si>
   <si>
-    <t>3.21x</t>
+    <t>3.20x</t>
   </si>
   <si>
     <t>Security Monitoring Details</t>
@@ -483,7 +483,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>780000000</v>
+        <v>777500000</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -491,7 +491,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2505679594</v>
+        <v>2484732976</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -565,19 +565,19 @@
         <v>19</v>
       </c>
       <c r="D4" s="3">
-        <v>556.85</v>
+        <v>548.15</v>
       </c>
       <c r="E4" s="4">
         <v>2066600</v>
       </c>
       <c r="F4" s="3">
-        <v>780000000</v>
+        <v>777500000</v>
       </c>
       <c r="G4" s="3">
-        <v>1150786210</v>
+        <v>1132806790</v>
       </c>
       <c r="H4" s="5">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="I4" s="5">
         <v>1</v>
@@ -597,16 +597,16 @@
         <v>21</v>
       </c>
       <c r="D5" s="3">
-        <v>497.72</v>
+        <v>496.63</v>
       </c>
       <c r="E5" s="4">
         <v>2722200</v>
       </c>
       <c r="F5" s="3">
-        <v>780000000</v>
+        <v>777500000</v>
       </c>
       <c r="G5" s="3">
-        <v>1354893384</v>
+        <v>1351926186</v>
       </c>
       <c r="H5" s="5">
         <v>1.74</v>
